--- a/forms/trg/Formulir_TRG_finra.xlsx
+++ b/forms/trg/Formulir_TRG_finra.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B38)</f>
+        <f>COUNTA(Anggota!B5:B39)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F38)</f>
+        <f>COUNTA(Anggota!F5:F39)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,31 +913,39 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Kartini Hanafi Idris, SE., M.Si., Ak.,CA., CRP., CRBC.</t>
+          <t>Prof. Dr. Darmawati, S.E., M.Si., Ak., CA., CRA., Asean CPA.</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Accounting</t>
+          <t>Financial Accounting, Government Accounting</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
-      <c r="J5" s="12" t="n"/>
-      <c r="K5" s="12" t="n"/>
-      <c r="L5" s="12" t="n"/>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>0000-0003-0536-3225</t>
+        </is>
+      </c>
+      <c r="K5" s="11" t="inlineStr">
+        <is>
+          <t>6038742</t>
+        </is>
+      </c>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>57204544475</t>
+        </is>
+      </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -950,12 +958,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Dr. Andi Kusumawati, S.E., M.Si., Ak., CA.</t>
+          <t>Prof. Dr. Kartini Hanafi Idris, SE., M.Si., Ak.,CA., CRP., CRBC.</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -965,28 +973,16 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Financial Accounting</t>
+          <t>Accounting</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="12" t="n"/>
       <c r="I6" s="12" t="n"/>
-      <c r="J6" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-9106-8320</t>
-        </is>
-      </c>
-      <c r="K6" s="11" t="inlineStr">
-        <is>
-          <t>6658554</t>
-        </is>
-      </c>
-      <c r="L6" s="11" t="inlineStr">
-        <is>
-          <t>56595092800</t>
-        </is>
-      </c>
+      <c r="J6" s="12" t="n"/>
+      <c r="K6" s="12" t="n"/>
+      <c r="L6" s="12" t="n"/>
       <c r="M6" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -999,12 +995,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Baginda Hamzah, S.T., M.B.A.</t>
+          <t>Dr. Andi Kusumawati, S.E., M.Si., Ak., CA.</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1012,18 +1008,30 @@
           <t>Hasanuddin University</t>
         </is>
       </c>
-      <c r="E7" s="11" t="n"/>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>Financial Accounting</t>
+        </is>
+      </c>
       <c r="F7" s="12" t="n"/>
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="12" t="n"/>
       <c r="I7" s="12" t="n"/>
-      <c r="J7" s="12" t="n"/>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-9106-8320</t>
+        </is>
+      </c>
       <c r="K7" s="11" t="inlineStr">
         <is>
-          <t>6933546</t>
-        </is>
-      </c>
-      <c r="L7" s="12" t="n"/>
+          <t>6658554</t>
+        </is>
+      </c>
+      <c r="L7" s="11" t="inlineStr">
+        <is>
+          <t>56595092800</t>
+        </is>
+      </c>
       <c r="M7" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1036,12 +1044,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Nirwana, S.E., M.Si., Ak., CA.</t>
+          <t>Baginda Hamzah, S.T., M.B.A.</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1049,30 +1057,18 @@
           <t>Hasanuddin University</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>Public Sector Accounting</t>
-        </is>
-      </c>
+      <c r="E8" s="11" t="n"/>
       <c r="F8" s="12" t="n"/>
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="12" t="n"/>
       <c r="I8" s="12" t="n"/>
-      <c r="J8" s="11" t="inlineStr">
-        <is>
-          <t>0000-0001-8608-9517</t>
-        </is>
-      </c>
+      <c r="J8" s="12" t="n"/>
       <c r="K8" s="11" t="inlineStr">
         <is>
-          <t>6026999</t>
-        </is>
-      </c>
-      <c r="L8" s="11" t="inlineStr">
-        <is>
-          <t>55977611800</t>
-        </is>
-      </c>
+          <t>6933546</t>
+        </is>
+      </c>
+      <c r="L8" s="12" t="n"/>
       <c r="M8" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1085,12 +1081,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Istiyansyah Ulman Idris, S.E., M.Sc. CRA., CRP.</t>
+          <t>Prof. Dr. Nirwana, S.E., M.Si., Ak., CA.</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1100,7 +1096,7 @@
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Financial Accounting</t>
+          <t>Public Sector Accounting</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1109,11 +1105,19 @@
       <c r="I9" s="12" t="n"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-7637-0735</t>
-        </is>
-      </c>
-      <c r="K9" s="12" t="n"/>
-      <c r="L9" s="12" t="n"/>
+          <t>0000-0001-8608-9517</t>
+        </is>
+      </c>
+      <c r="K9" s="11" t="inlineStr">
+        <is>
+          <t>6026999</t>
+        </is>
+      </c>
+      <c r="L9" s="11" t="inlineStr">
+        <is>
+          <t>55977611800</t>
+        </is>
+      </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1126,12 +1130,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Haniek Khoirunnissa Baja, S.E., M.Sc.</t>
+          <t>Muhammad Istiyansyah Ulman Idris, S.E., M.Sc. CRA., CRP.</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1150,14 +1154,10 @@
       <c r="I10" s="12" t="n"/>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>0009-0005-7682-4123</t>
-        </is>
-      </c>
-      <c r="K10" s="11" t="inlineStr">
-        <is>
-          <t>6783127</t>
-        </is>
-      </c>
+          <t>0000-0001-7637-0735</t>
+        </is>
+      </c>
+      <c r="K10" s="12" t="n"/>
       <c r="L10" s="12" t="n"/>
       <c r="M10" s="11" t="inlineStr">
         <is>
@@ -1171,22 +1171,22 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Noor Ismawati Binti Jafaar</t>
+          <t>Haniek Khoirunnissa Baja, S.E., M.Sc.</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Universiti Malaya</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>IT Governance, IT Management, Human Computer Interactions, Social Media Adoption</t>
+          <t>Financial Accounting</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -1195,15 +1195,15 @@
       <c r="I11" s="12" t="n"/>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-8604-6004</t>
-        </is>
-      </c>
-      <c r="K11" s="12" t="n"/>
-      <c r="L11" s="11" t="inlineStr">
-        <is>
-          <t>15848399900</t>
-        </is>
-      </c>
+          <t>0009-0005-7682-4123</t>
+        </is>
+      </c>
+      <c r="K11" s="11" t="inlineStr">
+        <is>
+          <t>6783127</t>
+        </is>
+      </c>
+      <c r="L11" s="12" t="n"/>
       <c r="M11" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1216,18 +1216,22 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Dr. Omar Mohamed Taha Alkanan ST.MT.</t>
+          <t>Prof. Dr. Noor Ismawati Binti Jafaar</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="n"/>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>Universiti Malaya</t>
+        </is>
+      </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>The Rosy City (Petra) for Educationa Services and Consultations</t>
+          <t>IT Governance, IT Management, Human Computer Interactions, Social Media Adoption</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -1236,13 +1240,13 @@
       <c r="I12" s="12" t="n"/>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>0009-0007-0944-9428</t>
+          <t>0000-0002-8604-6004</t>
         </is>
       </c>
       <c r="K12" s="12" t="n"/>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>59420580500</t>
+          <t>15848399900</t>
         </is>
       </c>
       <c r="M12" s="11" t="inlineStr">
@@ -1257,31 +1261,35 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Hernandi Julius Sousa Do Carmo</t>
+          <t>Dr. Omar Mohamed Taha Alkanan ST.MT.</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>Universidade Díli</t>
-        </is>
-      </c>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="n"/>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Accounting Science</t>
+          <t>The Rosy City (Petra) for Educationa Services and Consultations</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="12" t="n"/>
       <c r="H13" s="12" t="n"/>
       <c r="I13" s="12" t="n"/>
-      <c r="J13" s="12" t="n"/>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>0009-0007-0944-9428</t>
+        </is>
+      </c>
       <c r="K13" s="12" t="n"/>
-      <c r="L13" s="12" t="n"/>
+      <c r="L13" s="11" t="inlineStr">
+        <is>
+          <t>59420580500</t>
+        </is>
+      </c>
       <c r="M13" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1294,33 +1302,29 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Audrey Michelle Wenny Yolanda, S.E., M.Ac.</t>
+          <t>Hernandi Julius Sousa Do Carmo</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Universidade Díli</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Financial Accounting</t>
+          <t>Accounting Science</t>
         </is>
       </c>
       <c r="F14" s="12" t="n"/>
       <c r="G14" s="12" t="n"/>
       <c r="H14" s="12" t="n"/>
       <c r="I14" s="12" t="n"/>
-      <c r="J14" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-4929-5706</t>
-        </is>
-      </c>
+      <c r="J14" s="12" t="n"/>
       <c r="K14" s="12" t="n"/>
       <c r="L14" s="12" t="n"/>
       <c r="M14" s="11" t="inlineStr">
@@ -1335,12 +1339,12 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Asharin Juwita Purisamya, S.E., M.Si., ACPA.</t>
+          <t>Audrey Michelle Wenny Yolanda, S.E., M.Ac.</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -1350,7 +1354,7 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Financial Accounting, Sustainability Accounting</t>
+          <t>Financial Accounting</t>
         </is>
       </c>
       <c r="F15" s="12" t="n"/>
@@ -1359,14 +1363,10 @@
       <c r="I15" s="12" t="n"/>
       <c r="J15" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-9037-756X</t>
-        </is>
-      </c>
-      <c r="K15" s="11" t="inlineStr">
-        <is>
-          <t>6736159</t>
-        </is>
-      </c>
+          <t>0000-0002-4929-5706</t>
+        </is>
+      </c>
+      <c r="K15" s="12" t="n"/>
       <c r="L15" s="12" t="n"/>
       <c r="M15" s="11" t="inlineStr">
         <is>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Reza Pahlevi Juanda, S.E.</t>
+          <t>Asharin Juwita Purisamya, S.E., M.Si., ACPA.</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>Accounting, Auditing</t>
+          <t>Financial Accounting, Sustainability Accounting</t>
         </is>
       </c>
       <c r="F16" s="12" t="n"/>
@@ -1404,10 +1404,14 @@
       <c r="I16" s="12" t="n"/>
       <c r="J16" s="11" t="inlineStr">
         <is>
-          <t>0009-0001-9402-1181</t>
-        </is>
-      </c>
-      <c r="K16" s="12" t="n"/>
+          <t>0000-0002-9037-756X</t>
+        </is>
+      </c>
+      <c r="K16" s="11" t="inlineStr">
+        <is>
+          <t>6736159</t>
+        </is>
+      </c>
       <c r="L16" s="12" t="n"/>
       <c r="M16" s="11" t="inlineStr">
         <is>
@@ -1421,12 +1425,12 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Dr. Hj. A. Ratna Sari Dewi, S.E., M.Si, WPPE., WMI., CRA., CBOA.</t>
+          <t>Muhammad Reza Pahlevi Juanda, S.E.</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -1436,7 +1440,7 @@
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Financial Accounting</t>
+          <t>Accounting, Auditing</t>
         </is>
       </c>
       <c r="F17" s="12" t="n"/>
@@ -1445,19 +1449,11 @@
       <c r="I17" s="12" t="n"/>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-3893-8083</t>
-        </is>
-      </c>
-      <c r="K17" s="11" t="inlineStr">
-        <is>
-          <t>5991771</t>
-        </is>
-      </c>
-      <c r="L17" s="11" t="inlineStr">
-        <is>
-          <t>57205472442</t>
-        </is>
-      </c>
+          <t>0009-0001-9402-1181</t>
+        </is>
+      </c>
+      <c r="K17" s="12" t="n"/>
+      <c r="L17" s="12" t="n"/>
       <c r="M17" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1470,31 +1466,43 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Zul Fitrah Ramadhan, M.Pd.</t>
+          <t>Dr. Hj. A. Ratna Sari Dewi, S.E., M.Si, WPPE., WMI., CRA., CBOA.</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>State University of Makassar</t>
-        </is>
-      </c>
-      <c r="E18" s="11" t="n"/>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>Financial Accounting</t>
+        </is>
+      </c>
       <c r="F18" s="12" t="n"/>
       <c r="G18" s="12" t="n"/>
       <c r="H18" s="12" t="n"/>
       <c r="I18" s="12" t="n"/>
       <c r="J18" s="11" t="inlineStr">
         <is>
-          <t>0009-0002-8139-4509</t>
-        </is>
-      </c>
-      <c r="K18" s="12" t="n"/>
-      <c r="L18" s="12" t="n"/>
+          <t>0000-0002-3893-8083</t>
+        </is>
+      </c>
+      <c r="K18" s="11" t="inlineStr">
+        <is>
+          <t>5991771</t>
+        </is>
+      </c>
+      <c r="L18" s="11" t="inlineStr">
+        <is>
+          <t>57205472442</t>
+        </is>
+      </c>
       <c r="M18" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1507,43 +1515,31 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Andi Iqra Pradipta Natsir, S.E., M.Si., Ak., ACPA, CRA, CRP.</t>
+          <t>Zul Fitrah Ramadhan, M.Pd.</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
-      <c r="E19" s="11" t="inlineStr">
-        <is>
-          <t>Financial Accounting</t>
-        </is>
-      </c>
+          <t>State University of Makassar</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="n"/>
       <c r="F19" s="12" t="n"/>
       <c r="G19" s="12" t="n"/>
       <c r="H19" s="12" t="n"/>
       <c r="I19" s="12" t="n"/>
       <c r="J19" s="11" t="inlineStr">
         <is>
-          <t>0009-0008-8539-0795</t>
-        </is>
-      </c>
-      <c r="K19" s="11" t="inlineStr">
-        <is>
-          <t>6783251</t>
-        </is>
-      </c>
-      <c r="L19" s="11" t="inlineStr">
-        <is>
-          <t>59233539300</t>
-        </is>
-      </c>
+          <t>0009-0002-8139-4509</t>
+        </is>
+      </c>
+      <c r="K19" s="12" t="n"/>
+      <c r="L19" s="12" t="n"/>
       <c r="M19" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1556,12 +1552,12 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Haliah, SE., M.Si., Ak., CA., CRP., CRA., CWMA.</t>
+          <t>Andi Iqra Pradipta Natsir, S.E., M.Si., Ak., ACPA, CRA, CRP.</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
@@ -1571,7 +1567,7 @@
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>Accounting, Capital Markets</t>
+          <t>Financial Accounting</t>
         </is>
       </c>
       <c r="F20" s="12" t="n"/>
@@ -1580,17 +1576,17 @@
       <c r="I20" s="12" t="n"/>
       <c r="J20" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-7812-0502</t>
+          <t>0009-0008-8539-0795</t>
         </is>
       </c>
       <c r="K20" s="11" t="inlineStr">
         <is>
-          <t>6024022</t>
+          <t>6783251</t>
         </is>
       </c>
       <c r="L20" s="11" t="inlineStr">
         <is>
-          <t>56733007600</t>
+          <t>59233539300</t>
         </is>
       </c>
       <c r="M20" s="11" t="inlineStr">
@@ -1605,12 +1601,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>Indira Syakira Kirana Juanda</t>
+          <t>Prof. Dr. Haliah, SE., M.Si., Ak., CA., CRP., CRA., CWMA.</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
@@ -1620,7 +1616,7 @@
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Tax Accounting</t>
+          <t>Accounting, Capital Markets</t>
         </is>
       </c>
       <c r="F21" s="12" t="n"/>
@@ -1629,11 +1625,19 @@
       <c r="I21" s="12" t="n"/>
       <c r="J21" s="11" t="inlineStr">
         <is>
-          <t>0009-0002-6503-559X</t>
-        </is>
-      </c>
-      <c r="K21" s="12" t="n"/>
-      <c r="L21" s="12" t="n"/>
+          <t>0000-0001-7812-0502</t>
+        </is>
+      </c>
+      <c r="K21" s="11" t="inlineStr">
+        <is>
+          <t>6024022</t>
+        </is>
+      </c>
+      <c r="L21" s="11" t="inlineStr">
+        <is>
+          <t>56733007600</t>
+        </is>
+      </c>
       <c r="M21" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1646,22 +1650,22 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>Hamdani, SE., M.Si., Ak., CA.</t>
+          <t>Indira Syakira Kirana Juanda</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>Lambung Mangkurat University</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>Accounting</t>
+          <t>Tax Accounting</t>
         </is>
       </c>
       <c r="F22" s="12" t="n"/>
@@ -1670,14 +1674,10 @@
       <c r="I22" s="12" t="n"/>
       <c r="J22" s="11" t="inlineStr">
         <is>
-          <t>0009-0005-9610-4246</t>
-        </is>
-      </c>
-      <c r="K22" s="11" t="inlineStr">
-        <is>
-          <t>6710004</t>
-        </is>
-      </c>
+          <t>0009-0002-6503-559X</t>
+        </is>
+      </c>
+      <c r="K22" s="12" t="n"/>
       <c r="L22" s="12" t="n"/>
       <c r="M22" s="11" t="inlineStr">
         <is>
@@ -1691,17 +1691,17 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>Pusvita Indria Mei Susilowati</t>
+          <t>Hamdani, SE., M.Si., Ak., CA.</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Lambung Mangkurat University</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
@@ -1715,12 +1715,12 @@
       <c r="I23" s="12" t="n"/>
       <c r="J23" s="11" t="inlineStr">
         <is>
-          <t>0009-0004-0132-8371</t>
+          <t>0009-0005-9610-4246</t>
         </is>
       </c>
       <c r="K23" s="11" t="inlineStr">
         <is>
-          <t>6873830</t>
+          <t>6710004</t>
         </is>
       </c>
       <c r="L23" s="12" t="n"/>
@@ -1736,12 +1736,12 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>Nathania Pratiwi, S.Ak.</t>
+          <t>Pusvita Indria Mei Susilowati</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
@@ -1751,15 +1751,23 @@
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>Financial Accounting</t>
+          <t>Accounting</t>
         </is>
       </c>
       <c r="F24" s="12" t="n"/>
       <c r="G24" s="12" t="n"/>
       <c r="H24" s="12" t="n"/>
       <c r="I24" s="12" t="n"/>
-      <c r="J24" s="12" t="n"/>
-      <c r="K24" s="12" t="n"/>
+      <c r="J24" s="11" t="inlineStr">
+        <is>
+          <t>0009-0004-0132-8371</t>
+        </is>
+      </c>
+      <c r="K24" s="11" t="inlineStr">
+        <is>
+          <t>6873830</t>
+        </is>
+      </c>
       <c r="L24" s="12" t="n"/>
       <c r="M24" s="11" t="inlineStr">
         <is>
@@ -1773,12 +1781,12 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>Dr. Rahmawati HS, S.E., M.Si., Ak., CA.</t>
+          <t>Nathania Pratiwi, S.Ak.</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
@@ -1788,28 +1796,16 @@
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Financial Accounting, Government Accounting</t>
+          <t>Financial Accounting</t>
         </is>
       </c>
       <c r="F25" s="12" t="n"/>
       <c r="G25" s="12" t="n"/>
       <c r="H25" s="12" t="n"/>
       <c r="I25" s="12" t="n"/>
-      <c r="J25" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-1457-7914</t>
-        </is>
-      </c>
-      <c r="K25" s="11" t="inlineStr">
-        <is>
-          <t>6661679</t>
-        </is>
-      </c>
-      <c r="L25" s="11" t="inlineStr">
-        <is>
-          <t>57226838208</t>
-        </is>
-      </c>
+      <c r="J25" s="12" t="n"/>
+      <c r="K25" s="12" t="n"/>
+      <c r="L25" s="12" t="n"/>
       <c r="M25" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1822,12 +1818,12 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>Dr. Aini Indrijawati, S.E., M.Si., Ak., CA., CWM., Asean CPA.</t>
+          <t>Dr. Rahmawati HS, S.E., M.Si., Ak., CA.</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
@@ -1837,22 +1833,26 @@
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>Public Sector Accounting</t>
+          <t>Financial Accounting, Government Accounting</t>
         </is>
       </c>
       <c r="F26" s="12" t="n"/>
       <c r="G26" s="12" t="n"/>
       <c r="H26" s="12" t="n"/>
       <c r="I26" s="12" t="n"/>
-      <c r="J26" s="12" t="n"/>
+      <c r="J26" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-1457-7914</t>
+        </is>
+      </c>
       <c r="K26" s="11" t="inlineStr">
         <is>
-          <t>6009805</t>
+          <t>6661679</t>
         </is>
       </c>
       <c r="L26" s="11" t="inlineStr">
         <is>
-          <t>57215006464</t>
+          <t>57226838208</t>
         </is>
       </c>
       <c r="M26" s="11" t="inlineStr">
@@ -1865,18 +1865,46 @@
       <c r="A27" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="12" t="n"/>
-      <c r="C27" s="12" t="n"/>
-      <c r="D27" s="12" t="n"/>
-      <c r="E27" s="11" t="n"/>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>Dr. Aini Indrijawati, S.E., M.Si., Ak., CA., CWM., Asean CPA.</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>Public Sector Accounting</t>
+        </is>
+      </c>
       <c r="F27" s="12" t="n"/>
       <c r="G27" s="12" t="n"/>
       <c r="H27" s="12" t="n"/>
       <c r="I27" s="12" t="n"/>
       <c r="J27" s="12" t="n"/>
-      <c r="K27" s="12" t="n"/>
-      <c r="L27" s="12" t="n"/>
-      <c r="M27" s="12" t="n"/>
+      <c r="K27" s="11" t="inlineStr">
+        <is>
+          <t>6009805</t>
+        </is>
+      </c>
+      <c r="L27" s="11" t="inlineStr">
+        <is>
+          <t>57215006464</t>
+        </is>
+      </c>
+      <c r="M27" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -2065,15 +2093,32 @@
       <c r="L38" s="12" t="n"/>
       <c r="M38" s="12" t="n"/>
     </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="12" t="n"/>
+      <c r="C39" s="12" t="n"/>
+      <c r="D39" s="12" t="n"/>
+      <c r="E39" s="11" t="n"/>
+      <c r="F39" s="12" t="n"/>
+      <c r="G39" s="12" t="n"/>
+      <c r="H39" s="12" t="n"/>
+      <c r="I39" s="12" t="n"/>
+      <c r="J39" s="12" t="n"/>
+      <c r="K39" s="12" t="n"/>
+      <c r="L39" s="12" t="n"/>
+      <c r="M39" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
